--- a/daily_matches/job_matches_2026-06-01.xlsx
+++ b/daily_matches/job_matches_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026 Early Career – Gen AI – Data Science Analyst – United States, Atlanta (GA)</t>
+          <t>Senior Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>Bitdeer Technologies Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, AWS SageMaker, Snowflake, PySpark, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b16101ef1c145249</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce464c451a9c582</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Block Labs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Malta, MT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>Data Scientist, S3, Glue, Athena, Redshift, BigQuery, Kubernetes, Apache Airflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef82381c520011c</t>
+          <t>https://www.indeed.com/viewjob?jk=a8521c97662c0b57</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Onto Innovation</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, BigQuery, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,462 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762aab711b5e3031</t>
+          <t>https://www.indeed.com/viewjob?jk=c3a65fdc259b09f3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) - Retail</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SoftThink Solutions Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>West Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44a3e61f0ca766a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Software Engineer (Machine Learning)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51194abdd5a08da0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Software Developer - Simulation Platform (Galileo)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Redshift, BigQuery, BigQuery, Redshift, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d3552477f4c8d7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Credit Risk Analytics Specialist</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CRNCY Group</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, XGBoost, LightGBM, BigQuery, BigQuery, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3d691a831b5f69b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Entry Level Developer - Simulation Platform (Galileo)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Redshift, BigQuery, BigQuery, Redshift, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fbe75d978f8404c</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Incode Technologies</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b8ab2c2c6a0661a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior ML/AI Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Testamy AI System</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Snowflake, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26407ed64bc27a79</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Paramount</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Burbank, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65077fec1c61329c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, SQL, R, Julia, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e71e2c49d7fbc5fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, MySQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=367c6800280b4d85</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Architect (Onsite – Houston, TX)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Quanta Services</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ecf64d8510e1969</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c208306d500d82e</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Orion180 Insurance Services, LLC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faadbb95d5d4ea34</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Orion180 Insurance Services, LLC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=258607f4f5259139</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-01.xlsx
+++ b/daily_matches/job_matches_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud</t>
+          <t>Data &amp; AI Intern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bitdeer Technologies Group</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, Docker, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce464c451a9c582</t>
+          <t>https://www.indeed.com/viewjob?jk=e70e856c1968e4a1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Block Labs</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malta, MT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Athena, Redshift, BigQuery, Kubernetes, Apache Airflow, CI/CD, Terraform</t>
+          <t>RAG, S3, EC2, Glue, Redshift, Data Lake, Kinesis, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8521c97662c0b57</t>
+          <t>https://www.indeed.com/viewjob?jk=727aba117da7b7a0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, BigQuery, MLflow, CI/CD, Git</t>
+          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3a65fdc259b09f3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b20eb19409e2893</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>SDET (AI &amp; Next-Gen Automation)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SoftThink Solutions Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>West Sacramento, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Hugging Face, Prompt Engineering, Docker, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44a3e61f0ca766a1</t>
+          <t>https://www.indeed.com/viewjob?jk=950ffd42ea5b867f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer (Machine Learning)</t>
+          <t>Software Engineer (Co-op)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ribbon Communications</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, Docker, Kubernetes, Kafka, Hadoop, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51194abdd5a08da0</t>
+          <t>https://www.indeed.com/viewjob?jk=5a073e33a9128dc9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer - Simulation Platform (Galileo)</t>
+          <t>Specialist Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Redshift, BigQuery, BigQuery, Redshift, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, MLflow, Databricks, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3552477f4c8d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=27cc53924349f61c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Credit Risk Analytics Specialist</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CRNCY Group</t>
+          <t>AppCast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, LightGBM, BigQuery, BigQuery, Power BI, Python, SQL, R, Scala</t>
+          <t>Athena, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d691a831b5f69b</t>
+          <t>https://www.indeed.com/viewjob?jk=96b793539ad5d65c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Entry Level Developer - Simulation Platform (Galileo)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>AppCast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Redshift, BigQuery, BigQuery, Redshift, PostgreSQL, Python, SQL, R</t>
+          <t>Athena, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbe75d978f8404c</t>
+          <t>https://www.indeed.com/viewjob?jk=b128a04b14596e3a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Incode Technologies</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, Pinecone, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8ab2c2c6a0661a</t>
+          <t>https://www.indeed.com/viewjob?jk=eee68436e6a6959e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Testamy AI System</t>
+          <t>Material Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Snowflake, Databricks, Python, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Cortex, S3, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26407ed64bc27a79</t>
+          <t>https://www.indeed.com/viewjob?jk=a125832a9faf2b6d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Material Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Cortex, S3, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,102 +846,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65077fec1c61329c</t>
+          <t>https://www.indeed.com/viewjob?jk=13f4639de61892c3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Material Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, SQL, R, Julia, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Cortex, S3, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e71e2c49d7fbc5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf0998b173a8e22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>SmartTIX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, MySQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=367c6800280b4d85</t>
+          <t>https://www.indeed.com/viewjob?jk=a65fe6b467bcebd9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Architect (Onsite – Houston, TX)</t>
+          <t>Senior Software Engineer (Generalist)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Quanta Services</t>
+          <t>Traba</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c208306d500d82e</t>
+          <t>https://www.indeed.com/viewjob?jk=50bb20de9a6a3e7d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer (Generalist)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>Traba</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,42 +986,532 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faadbb95d5d4ea34</t>
+          <t>https://www.indeed.com/viewjob?jk=c0424ea793d01658</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>FP&amp;A Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>GALAXY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Git, Databricks, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23fb4d31a5ac4baf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026 Early Career – Gen AI – Data Science Analyst – United States, Atlanta (GA)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AIG</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, AWS SageMaker, Snowflake, PySpark, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ff9082a910c0bfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Backend (DocV)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84d2cdd9e9a41329</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Backend (DocV)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4448e7a7d6fdb939</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Backend (DocV)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03ea7856aad09922</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sr. Marketing Data Analyst</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WebstaurantStore</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Lititz, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af725f0d2890d81c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Technical Support Engineering</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GEVME</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, Git, MySQL, MongoDB, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33268d2023963c75</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DevOps Engineer II</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Renaissance Learning</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bloomington, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=788d322f9d8f2fd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Jr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Focus Camera</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, MySQL, Power BI, Python, SQL, R, Scala, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=328477616e982870</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer III, Forward Deployed</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>X-Energy</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Snowflake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=258607f4f5259139</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Docker, CI/CD, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb594fccccc3f2ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ML ops Engineer (local candidates only)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Health Data Analytics Institute</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Dedham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2661660998b6f1ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior DevSecOps Engineer | Financial Services | Plano, TX</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ideal Business Advisors</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc66b165ea58acb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data and Analytics Engineer III</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Praxis Precision Medicines, Inc.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c3c1bd3f9d14d41</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer (Generalist)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Traba</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78e5812a80947bce</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Cybersecurity Operations Engineer - AI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bread Financial</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Cortex, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1195735f7849ad12</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-01.xlsx
+++ b/daily_matches/job_matches_2026-06-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data &amp; AI Intern</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, Docker, CI/CD, Jenkins</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, EC2, Redshift, Data Lake, Kinesis, Redshift, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70e856c1968e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=34260a70256866e8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Software Engineer, AI Specialist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Redshift, Data Lake, Kinesis, Git, Snowflake, Databricks</t>
+          <t>LangChain, RAG, Gemini, Prompt Engineering, BigQuery, FastAPI, Docker, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727aba117da7b7a0</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a0b45e1676a63</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>GEN AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Git, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b20eb19409e2893</t>
+          <t>https://www.indeed.com/viewjob?jk=5a809974d84a7e76</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SDET (AI &amp; Next-Gen Automation)</t>
+          <t>Full Stack Software Engineer - Java</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Knott Cleaning</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Hugging Face, Prompt Engineering, Docker, CI/CD, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=950ffd42ea5b867f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a5aeeb93f9ed7b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer (Co-op)</t>
+          <t>Full-Stack Data BI Engineer (on-site)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ribbon Communications</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Docker, Kubernetes, Kafka, Hadoop, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Copilot, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a073e33a9128dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=83d0f91e0077746c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Specialist Data Scientist</t>
+          <t>Full-Stack Data BI Engineer (on-site)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, MLflow, Databricks, Python</t>
+          <t>AI Engineer, Copilot, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27cc53924349f61c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd42e61b1f00ae70</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AppCast</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athena, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Athena, Synapse, Data Lake, GitHub Actions, Git, PySpark, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b793539ad5d65c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4a9a916464c719</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AppCast</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athena, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Athena, Synapse, Data Lake, GitHub Actions, Git, PySpark, Power BI, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b128a04b14596e3a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c563ff6c6c61af</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>SkySlope</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, Pinecone, CI/CD, Terraform, Git, Python</t>
+          <t>RAG, S3, EC2, Jenkins, Terraform, Git, PostgreSQL, MySQL, MongoDB, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee68436e6a6959e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3139e590b6a0719</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Senior Machine Learning Engineer| Uber Direct</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Cortex, S3, Snowflake, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, CI/CD, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a125832a9faf2b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8ad0935585264e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Cortex, S3, Snowflake, Python, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, S3, Data Lake, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f4639de61892c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6a382e3d5a9c0a8a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Cortex, S3, Snowflake, Python, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, S3, Data Lake, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf0998b173a8e22</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7e9e84a12c3534</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SmartTIX</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, S3, Data Lake, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65fe6b467bcebd9</t>
+          <t>https://www.indeed.com/viewjob?jk=a75befce9107331c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Generalist)</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Traba</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, S3, Data Lake, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50bb20de9a6a3e7d</t>
+          <t>https://www.indeed.com/viewjob?jk=14cc48e7f7f837c5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Generalist)</t>
+          <t>DevOps Engineer - Security / PCI and Compliance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Traba</t>
+          <t>Edlio LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0424ea793d01658</t>
+          <t>https://www.indeed.com/viewjob?jk=324d5a4d0e21543e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FP&amp;A Data Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GALAXY</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Git, Databricks, Tableau, Python, SQL, R</t>
+          <t>RAG, Cortex, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23fb4d31a5ac4baf</t>
+          <t>https://www.indeed.com/viewjob?jk=14a047183f6fb10e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026 Early Career – Gen AI – Data Science Analyst – United States, Atlanta (GA)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, AWS SageMaker, Snowflake, PySpark, Python</t>
+          <t>AI Engineer, Generative AI, Gemini, Pinecone, Prompt Engineering, Docker, Kubernetes, Git, MongoDB, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff9082a910c0bfe</t>
+          <t>https://www.indeed.com/viewjob?jk=08444fb8b996544c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (DocV)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, Gemini, Pinecone, Prompt Engineering, Docker, Kubernetes, Git, MongoDB, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d2cdd9e9a41329</t>
+          <t>https://www.indeed.com/viewjob?jk=6723f885703823e2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (DocV)</t>
+          <t>RWD Delivery Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala</t>
+          <t>RAG, S3, Glue, Redshift, Data Lake, Apache Airflow, CI/CD, Git, Redshift, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4448e7a7d6fdb939</t>
+          <t>https://www.indeed.com/viewjob?jk=480648c59cb92063</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (DocV)</t>
+          <t>AL/ML Engineer / Azure Policy, AWS SCP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala</t>
+          <t>RAG, CI/CD, Terraform, Kafka, PostgreSQL, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7856aad09922</t>
+          <t>https://www.indeed.com/viewjob?jk=c3a5d8cf56d01694</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Marketing Data Analyst</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WebstaurantStore</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lititz, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, S3, EC2, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af725f0d2890d81c</t>
+          <t>https://www.indeed.com/viewjob?jk=476d52c54642bad6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Technical Support Engineering</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GEVME</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Git, MySQL, MongoDB, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Kubernetes, CI/CD, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33268d2023963c75</t>
+          <t>https://www.indeed.com/viewjob?jk=150c1c460a8f2243</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788d322f9d8f2fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=b255f7cfbea2f42a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jr. Data Scientist</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Focus Camera</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, MySQL, Power BI, Python, SQL, R, Scala, Optimization, Bayesian</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=328477616e982870</t>
+          <t>https://www.indeed.com/viewjob?jk=21d42f664c1bc212</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III, Forward Deployed</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>X-Energy</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, CI/CD, Terraform, Git, R, Java, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb594fccccc3f2ac</t>
+          <t>https://www.indeed.com/viewjob?jk=b23576df86210e6a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ML ops Engineer (local candidates only)</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2661660998b6f1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=268739eff36de340</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer | Financial Services | Plano, TX</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ideal Business Advisors</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, spaCy, FastAPI, Git, Python</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc66b165ea58acb1</t>
+          <t>https://www.indeed.com/viewjob?jk=853ce42179dfc224</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer III</t>
+          <t>AI Engineer (on-site)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Praxis Precision Medicines, Inc.</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, TensorFlow, PyTorch, MLflow, CI/CD, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3c1bd3f9d14d41</t>
+          <t>https://www.indeed.com/viewjob?jk=99038f3571c97ffc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer (Generalist)</t>
+          <t>AI Engineer (on-site)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Traba</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, TensorFlow, PyTorch, MLflow, CI/CD, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,42 +1476,1792 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e5812a80947bce</t>
+          <t>https://www.indeed.com/viewjob?jk=99495ea2e52817b3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Operations Engineer - AI</t>
+          <t>Senior Software Engineer, Cloud Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bread Financial</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4a5d383e49a299f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Quest Global</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Snowflake, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d614e5f53bf17a17</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Databricks, PySpark, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55697a169692173b</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Solutions Engineer(Python/Airflow)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EDB</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebdbfaeb882fcaf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Engineering Enablement</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4cbb85d400628e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Recognition Intelligence Applications</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Snowflake, PostgreSQL, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=126a91ef31ec8c04</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Fraud Data Infrastructure &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb32c3d561b71afc</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Fraud Data Infrastructure &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ccc2c386dcdad94</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Fraud Data Infrastructure &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ff18e89345b904e</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Fraud Data Infrastructure &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b23b51772175a04</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Backend / Systems Engineer (AI) - San Mateo, CA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Trustlab</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Kubernetes, CI/CD, Snowflake, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09c1fdaf23afab1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Cloud &amp; DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>First Orion</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>North Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, Terraform, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53bbcc678b9b2126</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PyTorch, S3, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d9272c185c23e1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PyTorch, S3, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=580e242948a318a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PyTorch, S3, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8c35a8039f2d699</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PyTorch, S3, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec4cb44123f0e681</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Digital Intelligence, Device Signals</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, XGBoost, Git, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dab90e01b4558724</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Digital Intelligence, Device Signals</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, XGBoost, Git, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98b4fe764ba8c7cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Digital Intelligence, Device Signals</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, XGBoost, Git, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d92f21e9c7b0648</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Digital Intelligence, Device Signals</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, XGBoost, Git, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63825c5ac86b8567</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DevOps Engineer II</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Renaissance Learning</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eabb7f6fbbd94f45</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RouteSmart Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Columbia, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, Docker, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aaff13e3e19c2343</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>RouteSmart Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Melville, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, Docker, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19d88c061ad9c5cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior AI Developer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Gene by Gene</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94224f3151a7b396</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, MLflow, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb9dd4339048dd48</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sr. Java Spring Boot Developer (OrderTech - Gemini) 2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>West Chester, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78f5909c9c1ee99b</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Snowflake Data Architect</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Keeley Construction</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Belleville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Cortex, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6593649772ba0f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Snowflake Data Architect</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Keeley Construction</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Edwardsville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Cortex, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef9a0c1b25b7c54d</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Snowflake Data Architect</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Keeley Construction</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Cortex, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e76b2adfe6dbb7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>GTM Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SolarWinds</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AI Engineer, Gemini, Prompt Engineering, BigQuery, AKS, BigQuery, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72488ca5c76f3a9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Software Engineer Data/AI/Intelligent Systems II (Intern) â€“ United States</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Hadoop, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=112dfedf0090a6e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
         <v>10</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Cortex, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1195735f7849ad12</t>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abd883707eedb645</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior GTM Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ambient.ai</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Glue, AKS, Snowflake, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d7f7c6aa8e98325</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Golang Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Stellar Solutions</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Kafka, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f89193dc23998066</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, PyTorch, MLflow, Databricks, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e43bcf4239102832</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AI Security Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Kubernetes, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b189efc79b9f280e</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Application Security Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c84843fe132672b</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Multi Media LLC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83e7621f8f4b6ce1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Vontas</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb54d60f52059053</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Data Analytics AI Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Fireblocks</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bf9d4983f7bf5e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer / Data Scientist</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Flagship Pioneering, Inc.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Hugging Face, PyTorch, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6615515e3042171</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Software and DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>VILLA-TECH, inc</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Naperville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, FastAPI, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01fca3261e03e685</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Product Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>hatch IT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f548607f4f474d43</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Borrow</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b979a02744a42b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Scientist II - Global Watchlist</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Data Scientist, Terraform, Git, Databricks, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00acdaf74b97aee8</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Data Scientist II - Global Watchlist</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Data Scientist, Terraform, Git, Databricks, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f6225655b5e07ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Data Scientist II - Global Watchlist</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Data Scientist, Terraform, Git, Databricks, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d69a089c5d2dc80</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Scientist II - Global Watchlist</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Data Scientist, Terraform, Git, Databricks, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e00313c67e7c938d</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Scientist 1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Waystar</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Data Scientist, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=990167a20e5a41e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Gaming Analytics</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Accel Entertainment Gaming, LLC.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Burr Ridge, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=671e077ce2bf0aee</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Gaming Analytics</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Accel Entertainment Gaming, LLC.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=447f4f88ea96fca2</t>
         </is>
       </c>
     </row>
